--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2687,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2752,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2817,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2882,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2947,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3077,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3142,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3207,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3272,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3337,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3463,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3589,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3715,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3902,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4028,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4154,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4219,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4345,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4410,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4536,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4601,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4849,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4914,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +4979,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5044,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5109,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5174,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5239,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5304,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5369,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5434,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5560,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5625,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5690,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5755,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5820,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5885,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5950,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6137,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6202,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6328,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6454,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6519,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6584,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6710,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6775,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6901,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7027,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7153,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7218,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7283,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7409,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7474,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7539,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7604,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7669,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7734,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7860,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7925,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +8055,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8120,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8185,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8250,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8376,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8441,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8628,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8693,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8758,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8823,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9071,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9258,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9323,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9049,7 +9449,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9514,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9579,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9644,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9709,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9835,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10083,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10148,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10274,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10400,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10526,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10147,7 +10591,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10717,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10782,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +10908,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +10973,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +11038,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +11103,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10696,7 +11168,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11233,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11298,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11363,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11428,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11001,7 +11493,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11558,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11688,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11753,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +11818,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +11944,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11493,7 +12009,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11554,7 +12074,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11676,7 +12200,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11737,7 +12265,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11859,7 +12391,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11981,7 +12517,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12042,7 +12582,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12103,7 +12647,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12225,7 +12773,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12286,7 +12838,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12469,7 +13025,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12530,7 +13090,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12591,7 +13155,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13220,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12713,7 +13285,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13350,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12835,7 +13415,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13480,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13545,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13610,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13675,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13384,7 +13984,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +14049,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13506,7 +14114,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13567,7 +14179,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14305,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13750,7 +14370,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13872,7 +14496,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13933,7 +14561,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14626,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14752,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +14817,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14299,7 +14943,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +15008,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14482,7 +15134,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14543,7 +15199,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14604,7 +15264,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
